--- a/scripts/nse_order_tracker_v2/output/orderbook_data.xlsx
+++ b/scripts/nse_order_tracker_v2/output/orderbook_data.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-29T00:14:25.340552</t>
+          <t>2026-05-29T00:19:07.476516</t>
         </is>
       </c>
     </row>

--- a/scripts/nse_order_tracker_v2/output/orderbook_data.xlsx
+++ b/scripts/nse_order_tracker_v2/output/orderbook_data.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-29T00:19:07.476516</t>
+          <t>2026-05-29T00:23:06.720141</t>
         </is>
       </c>
     </row>

--- a/scripts/nse_order_tracker_v2/output/orderbook_data.xlsx
+++ b/scripts/nse_order_tracker_v2/output/orderbook_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,22 +508,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LIKHITHA</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Likhitha Infrastructure Limited</t>
+          <t>Refex Industries Limited</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>₹121.04 Cr</t>
+          <t>₹36.91 Cr</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -531,15 +531,19 @@
           <t>Awarding of order(s)/contract(s)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Domestic entity</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LIKHITHA INFRASTRUCTURE LIMITED CIN : L35105TG1998PLC029911 Date: Thursday, May 28, 2026 To To The Corporate Relationship Department National Stock Exchange of India Ltd. BSE Limited Exchange Plaza, C-1, Block G, Phiroze Jeejeebhoy Towers Bandra Kurla Complex, Dalal Street Bandra (E) Mumbai- 400001 Mumbai — 400 051 Scrip Code: 543240 Stock Symbol: LIKHITHA Dear Sir/ Madam, Sub: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015. In terms of</t>
+          <t>May 29, 2026 BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers Exchange Plaza, Plot No. C-1, G Block, Dalal Street, Fort, Mumbai – 400001 Bandra-Kurla Complex, Bandra(E), Mumbai – 400051 Scrip Code: 532884 Symbol: REFEX RE: Disclosure under Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 ("SEBI Listing Regulations") read with SEBI Master Circular bearing reference no. HO/49/14/14(7)2025-C</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8-3-323</t>
+          <t>49/14/14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -548,12 +552,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://nsearchives.nseindia.com/corporate/LIKHITHA_28052026152431_Covering_Letter_Order.pdf</t>
+          <t>https://nsearchives.nseindia.com/corporate/REFEX2002_29052026125326_RILBaggingofOrder290526.pdf</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>downloads/nse_pdfs/LIKHITHA_2026-05-28.pdf</t>
+          <t>downloads/nse_pdfs/REFEX_2026-05-29.pdf</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -564,7 +568,3728 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-29T00:23:06.720141</t>
+          <t>2026-05-30T14:08:50.951208</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LIKHITHA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Likhitha Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>₹121.04 Cr</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LIKHITHA INFRASTRUCTURE LIMITED CIN : L35105TG1998PLC029911 Date: Thursday, May 28, 2026 To To The Corporate Relationship Department National Stock Exchange of India Ltd. BSE Limited Exchange Plaza, C-1, Block G, Phiroze Jeejeebhoy Towers Bandra Kurla Complex, Dalal Street Bandra (E) Mumbai- 400001 Mumbai — 400 051 Scrip Code: 543240 Stock Symbol: LIKHITHA Dear Sir/ Madam, Sub: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015. In terms of</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8-3-323</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/LIKHITHA_28052026152431_Covering_Letter_Order.pdf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/LIKHITHA_2026-05-28.pdf</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951216</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INNOVISION</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Date: 27/05/2026 To, To, The Manager The Manager, Listing Department Listing Department BSE Limited, National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, 5th Floor, Plot C/1, Dalal Street, Mumbai-400 001 G Block, Bandra-Kurla Complex BSE Code: 544732 Mumbai – 400 051. NSE Code: INNOVISION Dear Sir/Madam, Subject: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir / Madam, In accordance with the provis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INNOVISION2007_27052026184709_Work_Order_Intimation_270526_LH_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INNOVISION_2026-05-27.pdf</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951220</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ACMESOLAR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Acme Solar Holdings Limited</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>₹6.28 Cr</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>The a</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Leading Through Innovation M ay 26, 2026 To To BSE Limited National Stock Exchange of India Ltd Corporate Relationship Dept., Corporate Relationship Dept., Phiroze Jeejeebhoy Towers, Exchange Plaza, Plot No. C/1, G Block, Dalal Street, Mumbai 400001 Bandra-Kurla Complex, Bandra (East), Mumbai 400 051 Scrip Code: 544283 Symbol: ACMESOLAR Ref: Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015, as amended Subject: Executi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/ACMECS_26052026085800_Intimation26052026.pdf</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/ACMESOLAR_2026-05-26.pdf</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951235</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INNOVISION</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Date: 25/05/2026 To, To, The Manager The Manager, Listing Department Listing Department BSE Limited, National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, 5th Floor, Plot C/1, Dalal Street, Mumbai-400 001 G Block, Bandra-Kurla Complex BSE Code: 544732 Mumbai – 400 051. NSE Code: INNOVISION Dear Sir/Madam, Subject: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir / Madam, In accordance with the provis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INNOVISION2007_25052026181444_Work_Order_Intimation_250526_LH_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INNOVISION_2026-05-25.pdf</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951238</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MARSONS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Marsons Limited</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>₹0.31 Cr</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>US- based Solar Energy Developer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ref: M/3743/0006/2023 Date: 18/ 04/ 2023 (cid:9) To, Chief Engineer (O&amp;M-I) WBSETCL, Vidyut Bhavan , Date: 21.05.2026 Kolkata SubT:o O, ffer Sheet for the repairin g estim ates oTf oM, arsons Make” 630 kVA, 33/ 0.415 kV Station Service TraBnsSfEo rLmimerit eYdo m : 2008: (sl no: 82078 ) receivNeadt ioant afla Scttoocrky Epxrcehmainsegse ooff InMd/isa LMtda.r sons Limited on dt. 16.0P2h.i2ro0z2e3 Jeejeebhoy Towers Exchange Plaza, 5th Floor, Plot No. C/1 Dalal Street, G- block, Bandra- Kurla Compl</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MARSONS_21052026133641_BSEDisclosure.pdf</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MARSONS_2026-05-21.pdf</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951251</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Subex Limited</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>₹0.19 Cr</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>enhance</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>May 21, 2026 BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers Exchange Plaza, 5th Floor, Plot no. C/l Dalal Street, G Block, Bandra-Kurla Complex Mumbai- 400 001 Bandra (E), Mumbai - 400 051 BSE Scrip Code: 532348 NSE Symbol: SUBEXLTD Dear Sir/Madam, Sub: Disclosure under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Pursuant to Regulation 30 read with Para B of Part A of Schedule III of Securities and Exchange Board o</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/SUBEXLTD_21052026124046_Reg30OoradoAlgeria.pdf</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/SUBEXLTD_2026-05-21.pdf</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951254</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MAHEPC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Mahindra EPC Irrigation Limited</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>₹3.30 Cr</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mahindra EPC Irrigation Ltd. Plot No. H-109, MIDC, Ambad Nashik-422 010 India Tel: +91 253 6642000 Email: Info@mahindrairrigation.com www.mahindrairrigation.com 20th May, 2026 To, National Stock Exchange of India Limited BSE Limited, Exchange Plaza, C-I Block G, Phiroze Jeejeebhoy Towers, Bandra Kurla Complex, Bandra (East), Dalal Street, Fort, Mumbai 400051. Mumbai- 400 001. NSE Symbol: MAHEPC BSE Scrip Code: 523754 Sub.: Intimation under Regulation 30 of the Securities and Exchange Board of In</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MAHEPC_20052026095147_MEILReceiptofWorkOrder20052026.pdf</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MAHEPC_2026-05-20.pdf</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951260</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REMSONSIND</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Remsons Industries Limited</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>₹30.00 Cr</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>as Annexure-A.
+Kindly take the same on your record.
+Thanking you,
+Yours faithfully,</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>19th May, 2026 To, The Manager-Corporate Service Dept. The Manager-The Lis(cid:415)ng Department, BSE Limited Na(cid:415)onal Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, Bandra Kurla Complex, Dalal Street, Fort, Bandra (East), Mumbai – 400 001. Mumbai – 400051. Scrip code: 530919 Symbol: REMSONSIND Dear Sir / Ma’am, Sub: - In(cid:415)ma(cid:415)on pursuant to Regula(cid:415)on 30 of the SEBI (LODR) Regula(cid:415)ons, 2015 – new contracts / orders. Dear Sir / Ma’am</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/REMSONSIND_19052026124856_ORDER.pdf</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/REMSONSIND_2026-05-19.pdf</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951263</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GULPOLY</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Gulshan Polyols Limited</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>₹187072000.00 Cr</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Gulshan Polyols Limited CIN: L24231UP2000PLC034918 Corporate Office: G-81, Preet Vihar, Delhi-110092, India Phone : +91 11 49999200 Fax : +91 11 49999202 E-mail : cs@gulshanindia.com Website: www.gulshanindia.com GPL/SEC/08/2026-27 May 13, 2026 To, BSE Limited National Stock Exchange of India Limited Department of Corporate Service, Listing Department Floor 25, P. J. Towers, Exchange Plaza, Bandra Kurla Complex, Dalal Street, Mumbai Bandra (E), Mumbai Maharashtra- 400 001 Maharashtra-400 051 Scr</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/GULPOLY_13052026184622_Intimation13052026.pdf</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/GULPOLY_2026-05-13.pdf</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951273</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>UNIDT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>United Drilling Tools Limited</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>UNITED DRILLING TOOLS LTD. CIN : L29199DL1985PLC015796 OIL DRILLING EQUIPMENT MANUFACTURING AND SERVICES Phones : +91-120 – 4842400, Please Reply to Head Office - 4162715, 4729610 26th Floor, Astralis Tower, Supernova Fax No.: +91-120 – 2462675 Complex, Sector-94, Noida - 201301, USE PREFIX FOR CALLING Distt. G B Nagar,Uttar Pradesh, India From outside country – 91 – 120 E-mail : ENQUIRY@UDTLTD.COM From outside state – 0120 From New Delhi – 0120 Website : WWW.UDTLTD.COM 11/05/2026 UDT/SEC/2026-2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/UNIDT_11052026183822_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/UNIDT_2026-05-11.pdf</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951275</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INNOVISION</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>₹126654635.00 Cr</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Date: 09/05/2026 To, To, The Manager The Manager, Listing Department Listing Department BSE Limited, National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, 5th Floor, Plot C/1, Dalal Street, Mumbai-400 001 G Block, Bandra-Kurla Complex BSE Code: 544732 Mumbai – 400 051. NSE Code: INNOVISION Dear Sir/Madam, Subject: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir / Madam, In accordance with the provis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INNOVISION2007_09052026145726_Work_Order_Intimation_090526_LH_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INNOVISION_2026-05-09.pdf</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951278</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MARSONS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Marsons Limited</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>tank
+Un-tanking of Trans</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ref: M/3743/0006/2023 Date: 18/ 04/ 2023 (cid:9) To, Date: 08.05.2026 Chief Engineer (O&amp;M-I) WBSETCL, Vidyut Bhavan , Kolkata To, To, BSE Limited National Stock Exchange of India Ltd. Sub: Offer Sheet for the repairing estimates of Marsons Make” 630 kVA, 33/ 0.415 kV Station Service Phiroze Jeejeebhoy Towers Exchange Plaza, 5th Floor, Plot No. C/1 Transformer Yom: 2008: (sl no: 82078) received at factory premises of M/s Marsons Limited on dt. Dalal Street, G- block, Bandra- Kurla Complex 16.02.2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MARSONS_08052026131014_Reg_30_disclosure-_Ram_Taranga_order.pdf</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MARSONS_2026-05-08.pdf</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951280</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MIDWESTLTD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Midwest Limited</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>May 06, 2026 To, To, The Listing Department The Listing Department BSE Limited, National Stock Exchange of India Ltd., Phiroze Jeejeebhoy Towers, Exchange Plaza, Dalal Street, Bandra Kurla Complex, Bandra (East), Mumbai – 400001 Mumbai – 400051 Scrip Code: 544587 Symbol: MIDWESTLTD Dear Sir / Madam, Sub.: Intimation under Regulation 30 of SEBI (LODR) Regulations, 2015 – Selected as Lead Consortium Partner by Kerala Minerals and Metals Ltd. (KMML) for Strategic Rare Earth Elements Pilot Project P</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MIDWEST_06052026182532_award.pdf</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MIDWESTLTD_2026-05-06.pdf</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951282</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LIKHITHA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Likhitha Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>₹72.15 Cr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LIKHITHA INFRASTRUCTURE LIMITED CIN : L35105TG1998PLC029911 Date: Wednesday, May 06, 2026 To To The Corporate Relationship Department National Stock Exchange of India Ltd. BSE Limited Exchange Plaza, C-1, Block G, Phiroze Jeejeebhoy Towers Bandra Kurla Complex, Dalal Street Bandra (E) Mumbai- 400001 Mumbai — 400 051 Scrip Code: 543240 Stock Symbol: LIKHITHA Dear Sir/ Madam, Sub: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015. In terms o</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>8-3-323</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/LIKHITHA_06052026144841_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/LIKHITHA_2026-05-06.pdf</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951294</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GKENERGY</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GK Energy Limited</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>₹353.89 Cr</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Schedule III thereof, we
+would like to in</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Date: May 06, 2026 To, To, Listing Department Listing Department National Stock Exchange of India Limited BSE Limited Exchange Plaza, C-1, Block G, Phiroze Jeejeebhoy Towers, Bandra Kurla Complex Bandra (East), Dalal Street, Mumbai – 400 051 Mumbai – 400 001 NSE Symbol: GKENERGY Scrip Code BSE- 544525 Dear Sir/Madam, Subject: Announcement under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulation, 2015 (“SEBI Listing Regulations”) Pursuant to Regulation 30 of SEBI L</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/GKENERGY_06052026093259_pdf_sd.pdf</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/GKENERGY_2026-05-06.pdf</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951296</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>OSWALPUMPS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Oswal Pumps Limited</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>₹162.06 Cr</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Maharashtra State Electricity Distribution Company Limited</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>May 06, 2026 Listing Department Listing Department BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers Exchange Plaza, Bandra Kurla Complex Dalal Street Bandra (East) Mumbai – 400 001 Mumbai – 400051 Scrip Code: 544418 Name of Scrip: OSWALPUMPS Sub.: Disclosure under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 (‘Listing Regulations’) – Awarding of Order Dear Sir/ Madam, Pursuant to Regulation 30 of the Listing Regulations,</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/OSWALPUMPS_06052026084430_SELetterPMKusumOPL06052026.pdf</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/OSWALPUMPS_2026-05-06.pdf</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951298</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PIGL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Power &amp; Instrumentation (Gujarat) Limited</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>₹26192342.00 Cr</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>handling over of power supply system Electrical Work at Udaipur Air</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Power &amp; Instrumentation (Guj.) Limited AN ISO 9001 : 2008 COMPANY CIN : L32201G1983PLC006456 Date: 29t April, 2026 To, To, The National Stock Exchange of India Limited, BSE Limited Exchange Plaza, Floor 25, P. J. Towers Plot no. C/1, G Block, Dalal Street, Bandra-Kurla Complex Mumbai - 400 001 Bandra (E), Mumbai-400051 Scrip Symbol: PIGL Scrip Code:543912 Dear Sir/Madam, Sub: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Pursuant to Re</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>91-79-4005</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/PIGL_29042026183350_Disclosureunderregulation30OCR.pdf</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/PIGL_2026-04-29.pdf</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951306</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>INNOVISION</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Date: 25/04/2026 To, To, The Manager The Manager, Listing Department Listing Department BSE Limited, National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, 5th Floor, Plot C/1, Dalal Street, Mumbai-400 001 G Block, Bandra -Kurla Complex BSE Code: 544732 Mumbai – 400 051. NSE Code: INNOVISION Dear Sir/Madam, Subject: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir / Madam, In accordance with the provi</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INNOVISION2007_25042026193337_Work_Order_Intimation_25042026_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INNOVISION_2026-04-25.pdf</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951308</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>REPL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rudrabhishek Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/REPL_24042026184652_work_order_announcement.pdf</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/REPL_2026-04-24.pdf</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951319</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>INDIANHUME</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Indian Hume Pipe Company Limited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>₹417.97 Cr</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HP/SEC/2026/ 24th April, 2026 1. BSE Limited 2. National Stock Exchange of India Ltd. Corporate Relationship Department Exchange Plaza, 1 Floor, New Trading Ring, 5th Floor, Plot No. C/1, G-Block, st Round Bldg., Bandra Kurla Complex, Phiroze Jeejeebhoy Towers Bandra (East), Mumbai – 400051 Dalal Street, Mumbai – 400001 BSE Scrip Code: 504741 Symbol – INDIANHUME; Series EQ Dear Sirs, Sub: Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 - Work Order -----</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/SHARES_24042026173502_BSENSEINTIMATIONWORKORDERMAHARASHTRA24-04-2026.pdf</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INDIANHUME_2026-04-24.pdf</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951321</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ASHOKA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon Limited</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ashoka Buildcon Limited To To The Manager The Manager The Department of Corporate Services The Listing Department BSE Limited National Stock Exchange of India Limited Floor 25, P. J. Towers, Exchange Plaza, Bandra Kurla Complex, Dalal Street, Mumbai – 400 001 Bandra (East), Mumbai – 400 051 Scrip Code: Equity: 533271 Scrip Symbol: ASHOKA Debt Codes: CPs –730851/731112/731435/731487; and Debt Code NCDs: 976190 / 976191 / 976192 April 24, 2026 Subject: Receipt of Letter of Contract Acceptance from</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>92
+April 24</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/ASHOKA_24042026125704_485_ABL_BSE_NSE_Angola_LOA_24042026.pdf</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/ASHOKA_2026-04-24.pdf</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951331</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>INNOVISION</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Date: 22/04/206 To, To, The Manager The Manager, Listing Department Listing Department BSE Limited, National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, 5th Floor, Plot C/1, Dalal Street, Mumbai-400 001 G Block, Bandra-Kurla Complex BSE Code: 544732 Mumbai – 400 051. NSE Code: INNOVISION Dear Sir/Madam, Subject: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir / Madam, In accordance with the provisi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>22/04/206</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INNOVISION2007_22042026184725_Work_Order_Intimation_220426-vembukudi_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INNOVISION_2026-04-22.pdf</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951333</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UNIDT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>United Drilling Tools Limited</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>₹3.00 Cr</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>UNITED DRILLING TOOLS LTD. CIN : L29199DL1985PLC015796 OIL DRILLING EQUIPMENT MANUFACTURING AND SERVICES Phones : +91-120 – 4842400, Please Reply to Head Office - 4162715, 4729610 26th Floor, Astralis Tower, Supernova Fax No.: +91-120 – 2462675 Complex, Sector-94, Noida - 201301, USE PREFIX FOR CALLING Distt. G B Nagar,Uttar Pradesh, India From outside country – 91 – 120 E-mail : ENQUIRY@UDTLTD.COM From outside state – 0120 From New Delhi – 0120 Website : WWW.UDTLTD.COM 22/04/2026 UDT/SEC/2026-2</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/UNIDT_22042026115607_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/UNIDT_2026-04-22.pdf</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951335</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AEQUS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Aequs Limited</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>of AEPPL</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>April 20, 2026 To, National Stock Exchange of India Limited, BSE Limited, Exchange Plaza, C-1, Block G, 20th Floor, P.J. Towers, Bandra Kurla Complex, Bandra (E), Dalal Street, Mumbai – 400 051 Mumbai - 400001. NSE Scrip Symbol: AEQUS BSE Scrip Code: 544634 Subject: Intimation under Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir/ Ma’am, Pursuant to Regulation 30(6) of the Securities and Exchange Board of In</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/AEQUSLIMITED_20042026184348_Intiamtion_for_termination_of_orders_from_Hasbro.pdf</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/AEQUS_2026-04-20.pdf</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951337</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MARSONS</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Marsons Limited</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>₹153834500.00 Cr</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Inox Solar Limited</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ref: M/3743/0006/2023 Date: 18/ 04/ 2023 (cid:9) To, Date: 17.04.2026 Chief Engineer (O&amp;M-I) WBSETCL, Vidyut Bhavan , To, To, Kolkata BSE Limited National Stock Exchange of India Ltd. Phiroze Jeejeebhoy Towers Exchange Plaza, 5th Floor, Plot No. C/1 Sub: Offer Sheet for the repairing estimates of Marsons Make” 630 kVA, 33/ 0.415 kV Station Service Dalal Street, G- block, Bandra- Kurla Complex Transformer Yom: 2008: (sl no: 82078) received at factory premises of M/s Marsons Limited on dt. 16.0M2u</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MARSONS_17042026162458_Disclosure_under_Reg_30.pdf</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MARSONS_2026-04-17.pdf</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951346</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UNIDT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>United Drilling Tools Limited</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>UNITED DRILLING TOOLS LTD. CIN : L29199DL1985PLC015796 OIL DRILLING EQUIPMENT MANUFACTURING AND SERVICES Phones : +91-120 – 4842400, Please Reply to Head Office - 4162715, 4729610 26th Floor, Astralis Tower, Supernova Fax No.: +91-120 – 2462675 Complex, Sector-94, Noida - 201301, USE PREFIX FOR CALLING Distt. G B Nagar,Uttar Pradesh, India From outside country – 91 – 120 E-mail : ENQUIRY@UDTLTD.COM From outside state – 0120 From New Delhi – 0120 Website : WWW.UDTLTD.COM 16/04/2026 UDT/SEC/2026-2</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/UNIDT_16042026115150_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/UNIDT_2026-04-16.pdf</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951348</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>CONCOR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Container Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>₹175.36 Cr</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>- - ----- 1-11x81ll cf&gt;e.~x R~l'-1 fc;t~e.'5 ~~~ a (.:rRcl fl ·Um '&lt; cf1T '1 &lt;:Ix M '3 q &lt;'i&gt; S-J) cJ;i4ct,l-l CONCOR Container Corporation of India Ltd. cfR/~0ITT"m/SE/104/Vol.-VII/ A Multi-modal Logistics Company ~: 15.04.2026 (A N avratna CPSE of Govt. of India) The Bombay Stock Exchange Ltd., National Stock Exchange of India Ltd., Phiroze Jeejeebhoy Towers, Dalal Street Exchange Plaza, 5th Floor, Plot No. C/1, G Block, Mumbai-400001 Bandra-Kurla Complex, Bandra (E) Mumbai-400 051 (Through BS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>28/02/2027</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/CONCOR_15042026172803_CONCOR_SE_Reg30_Order.pdf</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/CONCOR_2026-04-15.pdf</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951358</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VRAJ</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vraj Iron and Steel Limited</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>g ,, _,+,x.:!+ii.i!"i VRAJ IRON AND STEEL LIMITED Formerly Known As VRAJ IRON AND STEEL pVT. LTD. &amp; PHIL ISPAT PRIVATE LIMITED Ref: VISL/SE/REG-30 12026-27 136 Date: April 13,2026 BSE Limited NSE Limited P.J. Towers, Exchange Plaza, C-1, Block G, Dalal Street, Fort Bandra Kurla Complex, Mumbai - 400001 Bandra (E), Mumbai - 400 051 Ref: BSE security code: 544204 NSE symbol: VRAJ Sub: Intimation under Reeulation 30 of SEBI (LODR) Reeulations. 2015 - Grant of Electricitv Duty Exemption for Captive</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/VISL_13042026163043_Solar_Exemption_VISL.pdf</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/VRAJ_2026-04-13.pdf</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951369</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HBL Engineering Limited</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>₹83.81 Cr</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>CIN: L40109TG1986PLCO06745 - ® D.No. 8-2-616, Plot No. 4, B L Behind Minerva Grand Hotel, Road No. 11, Banjaa Hils, HBL ENGINEERING LIMITED - 4, T.S., INDIA :K::;a‘?afg1§23-gg?%;777 (Formerly known as HBL Power Systems Limited) Date: April 09, 2026 The Listing Department The Department of Corporate Services National Stock Exchange of India Limited BSE Limited Exchange Plaza, Bandra Kurla Complex Phiroze Jeejeebhoy Towers Bandra (East), Mumbai — 400 051 Dalal Street, Mumbai — 400 001 NSE CODE: HB</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8-2-616</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/HBLPOWER_09042026101653_ilovepdfmerged.pdf</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/HBLENGINE_2026-04-09.pdf</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951379</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HBLENGINE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HBL Engineering Limited</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>₹83.81 Cr</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>CIN: L40109TG1986PLCO06745 - ® D.No. 8-2-616, Plot No. 4, B L Behind Minerva Grand Hotel, Road No. 11, Banjaa Hils, HBL ENGINEERING LIMITED - 4, T.S., INDIA :K::;a‘?afg1§23-gg?%;777 (Formerly known as HBL Power Systems Limited) Date: April 09, 2026 The Listing Department The Department of Corporate Services National Stock Exchange of India Limited BSE Limited Exchange Plaza, Bandra Kurla Complex Phiroze Jeejeebhoy Towers Bandra (East), Mumbai — 400 051 Dalal Street, Mumbai — 400 001 NSE CODE: HB</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>8-2-616</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/HBLPOWER_09042026085125_KavachOrder08April2026.pdf</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/HBLENGINE_2026-04-09.pdf</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951380</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>INNOVISION</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Innovision Limited</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>₹993529635.00 Cr</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Date: 08/04/2026 To, To, The Manager The Manager, Listing Department Listing Department BSE Limited, National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, 5th Floor, Plot C/1, Dalal Street, Mumbai-400 001 G Block, Bandra-Kurla Complex BSE Code: 544732 Mumbai – 400 051. NSE Code: INNOVISION Dear Sir/Madam, Subject: Intimation under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Dear Sir / Madam, In accordance with the provis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INNOVISION2007_08042026155948_Work_Order_Intimation_080426_LH_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INNOVISION_2026-04-08.pdf</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951383</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PROSTARM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Prostarm Info Systems Limited</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>₹165.00 Cr</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Solarium Green Energy Limited</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Prostarm/Secretarial/2026-27/05 April 07, 2026 To, BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, C-1, Block G, Dalal Street, Mumbai – 400 001 Bandra Kurla Complex, Bandra (E), Mumbai – 400 051 Scrip Code: 544410 Scrip Symbol: PROSTARM Sub: LOA from Solarium Green Energy Limited for execution of End -to-End EPC works for 50 MWac Solar PV Power Project in the State of Maharashtra Ref: Regulation 30 of the Securities and Exchange Board of India (Lis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>26-27/05</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/PROSTARM_07042026180737_SE_LOA.pdf</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/PROSTARM_2026-04-07.pdf</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951385</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DEEPINDS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deep Industries Limited</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>₹59.00 Cr</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>reference to the captioned subject, we would like to in</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>April 06, 2026 To, To, Corporate Relations Department Corporate Relations Department BSE Limited National Stock Exchange of India Ltd. 2nd Floor, P.J. Towers, Exchange Plaza, Plot No. C/1, G-Block, Dalal Street, Bandra Kurla Complex, Bandra (E), Mumbai – 400 001 Mumbai – 400051. SCRIP CODE: 543288 SYMBOL: DEEPINDS Sub: Intimation under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulation, 2015- Announcement in respect of Letter of Award received from Oil and Nat</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/DEEPINDS_06042026181300_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/DEEPINDS_2026-04-06.pdf</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951397</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UNIDT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>United Drilling Tools Limited</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>UNITED DRILLING TOOLS LTD. CIN : L29199DL1985PLC015796 OIL DRILLING EQUIPMENT MANUFACTURING AND SERVICES Phones : +91-120 – 4842400, Please Reply to Head Office - 4162715, 4729610 26th Floor, Astralis Tower, Supernova Fax No.: +91-120 – 2462675 Complex, Sector-94, Noida - 201301, USE PREFIX FOR CALLING Distt. G B Nagar,Uttar Pradesh, India From outside country – 91 – 120 E-mail : ENQUIRY@UDTLTD.COM From outside state – 0120 From New Delhi – 0120 Website : WWW.UDTLTD.COM 06/04/2025 UDT/SEC/2026-2</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>06/04/2025</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/UNIDT_06042026174926_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/UNIDT_2026-04-06.pdf</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951399</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>₹426820821.94 Cr</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Date: 3rd April, 2026 To, Manager - Listing Compliance Corporate Relationship Department, National Stock Exchange of India Limited BSE Limited, ‘Exchange Plaza’. C-1, Block G, P.J. Towers, Dalal Street, Bandra Kurla Complex, Bandra (E), Fort, Mumbai - 400001 Mumbai - 400 051 Scrip Code: 544281 Symbol: ABINFRA ISIN: INE00YB01025 Dear Sir/ Madam, Subject: Reg. 30 of SEBI (LODR) Regulations, 2015. In accordance with the provision of Regulation 30 of SEBI (LODR) Regulations, 2015, we hereby intimate</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>62/9-11</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/ABINFRA_03042026115023_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/ABINFRA_2026-04-03.pdf</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951409</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TITAGARH RAIL SYSTEMS LIMITED</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>₹44.41 Cr</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Schedule III of the Listing Regulations, we wish to in</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>26th March 2026 BSE Limited (BSE) National Stock Exchange of India Limited (NSE) The Department of Corporate Services The Listing Compliance Department Phiroze Jeejeebhoy Towers Exchange Plaza Bandra-Kurla Complex Dalal Street, Mumbai – 400 001 Bandra (E), Mumbai – 400 051 Scrip Code: 532966 Symbol: TITAGARH Dear Sir/Madam, Sub: Disclosure under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations 2015 (‘Listing Regulations’) - “Receipt of Letter of Intent for appo</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/TWL_26032026203359_DisclosuretoSELOI26032026.pdf</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/TITAGARH_2026-03-26.pdf</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951420</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WEWIN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>WE WIN LIMITED</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>₹194400000.00 Cr</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>WW/ we win WWL/CS/2025-26/131 Date: 26t March, 2026 National Stock Exchange of India Limited BSE Limited E Bax nc dh ra an -g e K uP rl la az a, C oP ml po lt exN ,o. BC a n/1 d, r aG (B El ) ock, Floor 25, P.J Towers, Dalal Street, Fort, Mumbai- 400001 Mumbai-400051 BSE Scrip Code: 543535 NSE Symbol: WEWIN Sub: - Regarding Award of Work Order for Selection of Bidder for Implementation of CM Helpline &amp; Complaint Management System for Chhattisgarh. Dear Sir/Madam, In compliance with Regulation 30</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>25-26/131</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/SUREVIN_26032026114355_IntimationCMHelplineChhattisgarh26032026.pdf</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/WEWIN_2026-03-26.pdf</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951429</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cholamandalam Investment and Finance Company Limited</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>₹540.00 Cr</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>25 March, 2026 The Secretary The Secretary National Stock Exchange of India Limited BSE Ltd. Trade World, 4th Floor, 1st Floor, P.J. Towers Kamala Mills Compound, Dalal Street, Fort, Senapati Bapat Marg, Lower Parel, Mumbai 400 001 Mumbai 400 013 NSE SCRIP CODE: CHOLAFIN EQ BSE SCRIP CODE: 511243 Dear Sir/ Madam, Sub: Intimation under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 (‘SEBI Listing Regulations) Pursuant to Regulation 30 of the SEBI Lis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/lakshmits_25032026190550_Intimation_Contracts_25Mar2026.pdf</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/CHOLAFIN_2026-03-25.pdf</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951439</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GRINFRA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>G R Infraprojects Limited</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>rd 23 March 2026 BSE Limited National Stock Exchange of India Limited To Phiroze Jeejeebhoy Towers Exchange Plaza, Plot No. C-1 DScarlaipl SCtoredeet:, 5Fo4r3t3 17 GSy Bmlobcokl,: B GaRnIdNrFa-RKAu rla Complex, Bandra(E) Mumbai – 400001 Mumbai -400051 Subject: G R Infraprojects Limited has received Letter of Award (“LOA”) for the project “Construction of 4 lane Greenfield Section of NH-33 from Mokama (Design Ch. 0+000) to Munger (Design Ch. 82+400) in the State of Bihar on Hybrid Annuity Mode.”</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>23 March 2026</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/GRINFRA_23032026165409_LOA_23032026.pdf</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/GRINFRA_2026-03-23.pdf</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951449</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DBREALTY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Valor Estate Limited</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>₹108.00 Cr</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Date : 19th March, 2026 The General Manager, The Vice-President, Listing Department Listing Department BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, “Exchange Plaza”, Dalal Street, Bandra – Kurla Complex, Mumbai 400 001 Bandra (E), Mumbai – 400 051 Scrip Code : 533160 Scrip Symbol : DBREALTY Dear Sir/Madam, Subject: Letter of Award issued by the Government of Goa (Department of Public Private Partnership) to the Company for development of an International Conven</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/DBR_19032026125956_VEL_SE_Intimation_Letter_of_Award.pdf</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/DBREALTY_2026-03-19.pdf</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951459</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CESC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CESC Limited</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>₹25.00 Cr</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>relevant circulars issued by the Securities
+and Exchange Board of India, we would like to in</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DOC:SEC:1716/2025-26/383 March 17, 2026 National Stock Exchange of India Limited BSE Limited Exchange Plaza, 5th Floor, Plot No. C/1, Phiroze Jeejeebhoy Towers, G- Block, Bandra – Kurla Complex, Dalal Street, Bandra (East), Mumbai – 400 001 Mumbai – 400 051 SCRIP CODE: 500084 SCRIP CODE: CESC Dear Sir/ Madam, Disclosure under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Pursuant to Regulation 30 of the Securities and Exchange Board of India (Listi</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>25-26/383</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/CESC_17032026202757_1.pdf</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/CESC_2026-03-17.pdf</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951466</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>₹486775280.22 Cr</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Date: 17th March, 2026 To, Manager - Listing Compliance Corporate Relationship Department, National Stock Exchange of India Limited BSE Limited, ‘Exchange Plaza’. C-1, Block G, P.J. Towers, Dalal Street, Bandra Kurla Complex, Bandra (E), Fort, Mumbai - 400001 Mumbai - 400 051 Scrip Code: 544281 Symbol: ABINFRA ISIN: INE00YB01025 Dear Sir/ Madam, Subject: Reg. 30 of SEBI (LODR) Regulations, 2015. In accordance with the provision of Regulation 30 of SEBI (LODR) Regulations, 2015, we hereby intimat</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/ABINFRA_17032026164234_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/ABINFRA_2026-03-17.pdf</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951473</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Subex Limited</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>₹0.27 Cr</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>March 17, 2026 BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers Exchange Plaza, 5th Floor, Plot no. C/l Dalal Street, G Block, Bandra-Kurla Complex Mumbai- 400 001 Bandra (E), Mumbai - 400 051 BSE Scrip Code: 532348 NSE Symbol: SUBEXLTD Dear Sir/Madam, Sub: Disclosure under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Pursuant to Regulation 30 read with Para B of Part A of Schedule III of Securities and Exchange Board</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/SUBEXLTD_17032026154904_Disclosure17032026.pdf</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/SUBEXLTD_2026-03-17.pdf</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951476</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PROSTARM</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Prostarm Info Systems Limited</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>₹90.44 Cr</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Prostarm/Secretarial/2025-26/99 March 17, 2026 To, BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, C-1, Block G, Dalal Street, Mumbai – 400 001 Bandra Kurla Complex, Bandra (E), Mumbai – 400 051 Scrip Code: 544410 Scrip Symbol: PROSTARM Sub: Company has been declared as L-1 bidder by West Bengal Medical Services Corporation (WBMSC), Kolkata Ref: Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirem</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>25-26/99</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/PROSTARM_17032026114624_SE_L1___WBMSC__WB.pdf</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/PROSTARM_2026-03-17.pdf</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951478</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MAHEPC</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mahindra EPC Irrigation Limited</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>₹17.95 Cr</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>16th March, 2026 National Stock Exchange of India Limited BSE Limited, Exchange Plaza, C-I Block G, Phiroze Jeejeebhoy Towers, Bandra Kurla Complex, Bandra (East), Dalal Street, Fort, Mumbai 400051. Mumbai- 400 001. NSE Symbol: MAHEPC BSE Scrip Code: 523754 Sub.: Intimation under Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements) Regulations, 2015 – Award of Contract Dear Sir / Madam, In terms of Regulations 30(3), 30(4) read with Para B</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MAHEPC_16032026133114_Intimation_under_Reg30.pdf</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MAHEPC_2026-03-16.pdf</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951486</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PROSTARM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Prostarm Info Systems Limited</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>₹6.71 Cr</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Prostarm/Secretarial/2025-26/98 March 13, 2026 To, BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, C-1, Block G, Dalal Street, Mumbai – 400 001 Bandra Kurla Complex, Bandra (E), Mumbai – 400 051 Scrip Code: 544410 Scrip Symbol: PROSTARM Sub: LOA from SAIL for Supply, installation &amp; commissioning of 2 MW Roof Top Solar Project Ref: Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements Regulation</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>25-26/98</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/PROSTARM_13032026175311_SE_SAIL_LOA.pdf</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/PROSTARM_2026-03-13.pdf</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951496</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PROSTARM</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Prostarm Info Systems Limited</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>₹6.71 Cr</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Prostarm/Secretarial/2025-26/98 March 13, 2026 To, BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers, Exchange Plaza, C-1, Block G, Dalal Street, Mumbai – 400 001 Bandra Kurla Complex, Bandra (E), Mumbai – 400 051 Scrip Code: 544410 Scrip Symbol: PROSTARM Sub: LOA from SAIL for Supply, installation &amp; commissioning of 2 MW Roof Top Solar Project Ref: Regulation 30 of the Securities and Exchange Board of India (Listing Obligations and Disclosure Requirements Regulation</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>25-26/98</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/PROSTARM_13032026174451_SE_SAIL_LOA.pdf</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/PROSTARM_2026-03-13.pdf</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951498</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>₹669624916.57 Cr</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Date: 13th March, 2026 To, Manager - Listing Compliance Corporate Relationship Department, National Stock Exchange of India Limited BSE Limited, ‘Exchange Plaza’. C-1, Block G, P.J. Towers, Dalal Street, Bandra Kurla Complex, Bandra (E), Fort, Mumbai - 400001 Mumbai - 400 051 Scrip Code: 544281 Symbol: ABINFRA ISIN: INE00YB01025 Dear Sir/ Madam, Subject: Reg. 30 of SEBI (LODR) Regulations, 2015. In accordance with the provision of Regulation 30 of SEBI (LODR) Regulations, 2015, we hereby intimat</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>29/11-13</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/ABINFRA_13032026163329_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/ABINFRA_2026-03-13.pdf</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951500</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>INDOWIND</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Indowind Energy Limited</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>₹84.33 Cr</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>the appointed date as specified in the scheme, upon filing of the NCLT
+order with the Registrar of Companies through e-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>13th March, 2026 BSE LIMITED NATIONAL STOCK EXCHANGE The General Manager, OF INDIA LIMITED The Corporate Relation Department, Listing Department Phiroze Jeejoybhoy Tower, Exchange Plaza, Bandra Kurla 44+ Floor, Dalal Street, Complex, -Bandra (E), Mumbai — 400 001 Mumbai — 400 051 Scrip Code: 532894 NSE Symbol: INDOWIND Dear Sir / Madam, Sub: Sanction of the Scheme by the Hon’ble National Company Law Tribunal (“NCLT”) [Intimation under Regulation 30 of the SEBI (Listing Obligations and Disclosure</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/INDOWIND_13032026133426_CML.pdf</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/INDOWIND_2026-03-13.pdf</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951510</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MAHEPC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Mahindra EPC Irrigation Limited</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>₹2.22 Cr</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Mahindra EPC Irrigation Ltd. Plot No. H-109, MIDC, Ambad Nashik-422 010 India Tel: +91 253 6642000 Email: Info@mahindrairrigation.com www.mahindrairrigation.com 12th March, 2026 National Stock Exchange of India Limited BSE Limited, Exchange Plaza, C-I Block G, Phiroze Jeejeebhoy Towers, Bandra Kurla Complex, Bandra (East), Dalal Street, Fort, Mumbai 400051. Mumbai- 400 001. NSE Symbol: MAHEPC BSE Scrip Code: 523754 Sub.: Intimation under Regulation 30 of the Securities and Exchange Board of Indi</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/MAHEPC_12032026172525_Intimation_under_Reg_30_13-03-2026.pdf</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/MAHEPC_2026-03-12.pdf</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951519</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VASCONEQ</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Vascon Engineers Limited</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>₹1159028904.00 Cr</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ahmedabad Municipal Corporation</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>March 11, 2026 To, To, National Stock Exchange of India Limited BSE Limited Listing Department, The Department of Corporate Services Exchange Plaza, Phiroze Jeejeebhoy Towers, Dalal Street, Bandra (E), Mumbai – 400 051 Fort, Mumbai 400 001 Ref Symbol: VASCONEQ Ref: Scrip Code: 533156 Subject: Vascon Engineers Limited receives Letter of Intent - Development of Lotus Park on 54,000 Sq. Mtrs, South West Zone under Building Project of Ahmedabad Municipal Corporation, Ahmedabad Ref: Disclosure under</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/VASCONEQ_11032026163946_11032026LetterofIntent.pdf</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/VASCONEQ_2026-03-11.pdf</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951529</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DBL</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Dilip Buildcon Limited</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>₹1850.00 Cr</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>REC Power Development and Consultancy Limited</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>March 11, 2026 To BSE Limited National Stock Exchange of India Ltd. Phiroze Jeejeebhoy Towers Exchange Plaza, C-1, Block G, Dalal Street Bandra Kurla Complex, Mumbai- 400001 Bandra (E) Mumbai – 400 051 Scrip Code – 540047 Scrip Code – DBL Sub: Intimation of receipt of Letter of Intent (LOI) from REC Power Development and Consultancy Limited for “Establishing 400 kV Sub-station at Mekhali along with associated transmission lines (Belagavi District), Karnataka”. In continuation of our announcement</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/DBL_11032026114556_Announcement.pdf</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/DBL_2026-03-11.pdf</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951538</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PROTEAN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Protean eGov Technologies Limited</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>₹226025562.00 Cr</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>protean Ref: Protean/Secretarial/2025-26/111 March 10, 2026 To, BSE Limited (“BSE”) National Stock Exchange of India Limited P.J. Towers, Dalal Street, Exchange Plaza, C-1, Block G, Fort, Mumbai – 400 001 Bandra Kurla Complex, Bandra (E), Mumbai – 400051, India Scrip Code: 544021 Trading symbol: PROTEAN Dear Sir/Madam, Subject: Disclosure under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 Pursuant to Regulation 30 read with Schedule III and other</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>25-26/111</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/PROTEANCS_10032026192822_Intimation_-_MVAT_CST_order.pdf</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/PROTEAN_2026-03-10.pdf</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951547</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BMWVENTLTD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BMW Ventures Limited</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>₹15.91 Cr</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>on account of</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>BMW VENTURES LIMITED Date - March 10, 2026 To, o, Listing Department Listing Department BSE Limited National Stock Exchange of India Limited, Exchange Plaza, C-1, Block G, Bandra Phiroze Jeejeebhoy Towers, Dalal Street, Kurla Complex, Bandra (E), Mumbai — Mumbai — 400001 400051 Script Code: 544543 Symbol: BMWVENTLTD Sub: Disclosure under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 (“SEBI Listing Regulations”) Dear Sir/Madam, Pursuant to the provi</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/BMWVENTURES2024_10032026135123_PEB_ORDER.pdf</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/BMWVENTLTD_2026-03-10.pdf</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951557</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>UNIDT</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>United Drilling Tools Limited</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>UNITED DRILLING TOOLS LTD. CIN : L29199DL1985PLC015796 OIL DRILLING EQUIPMENT MANUFACTURING AND SERVICES Phones : +91-120 – 4842400, Please Reply to Head Office - 4162715, 4729610 26th Floor, Astralis Tower, Supernova Fax No.: +91-120 – 2462675 Complex, Sector-94, Noida - 201301, USE PREFIX FOR CALLING Distt. G B Nagar,Uttar Pradesh, India From outside country – 91 – 120 E-mail : ENQUIRY@UDTLTD.COM From outside state – 0120 From New Delhi – 0120 Website : WWW.UDTLTD.COM 07/03/2026 UDT/SEC/2025-2</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>07/03/2026</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/UNIDT_07032026125345_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/UNIDT_2026-03-07.pdf</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951567</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>₹629404813.35 Cr</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Date: 4th March, 2026 To, Manager - Listing Compliance Corporate Relationship Department, National Stock Exchange of India Limited BSE Limited, ‘Exchange Plaza’. C-1, Block G, P.J. Towers, Dalal Street, Bandra Kurla Complex, Bandra (E), Fort, Mumbai - 400001 Mumbai - 400 051 Scrip Code: 544281 Symbol: ABINFRA ISIN: INE00YB01025 Dear Sir/ Madam, Subject: Reg. 30 of SEBI (LODR) Regulations, 2015. In accordance with the provision of Regulation 30 of SEBI (LODR) Regulations, 2015, we hereby intimate</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/ABINFRA_04032026112922_Intimation.pdf</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/ABINFRA_2026-03-04.pdf</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951576</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>JUNIPER</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Juniper Hotels Limited</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Not found</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>JHL/SJ/2026/17 March 03, 2026 National Stock Exchange of India Limited BSE Limited, Exchange Plaza, Corporate Relationship Department Bandra Kurla Complex, Phiroze Jeejeebhoy Towers, BSyamndbroal (: EJUasNt)I,P ER DScarlaipl SCtoredeet:, 5Fo4r4t1, 29 Mumbai - 400 051 Mumbai - 400 001 Subject: Disclosure under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 (“SEBI Listing Regulations”)- Receipt of Letter of Award from Delhi Development Authority (“DDA</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>17 March 03</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/9930371292_03032026162217_Letter-signed.pdf</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/JUNIPER_2026-03-03.pdf</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951585</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3IINFOLTD</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3i Infotech Limited</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>₹3.19 Cr</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>a leading Asset Management Company in India</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>March 2, 2026 BSE Limited National Stock Exchange of India Limited Sir Phiroze Jeejeebhoy Towers Exchange Plaza, 5th Floor, Dalal Street, Fort, Plot No. C-1, Block G Mumbai – 400 001 Bandra Kurla Complex, Security Code: 532628 Mumbai – 400 051 Scrip code: 3IINFOLTD Dear Sir/Madam, Sub: Intimation under Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 – Award of Order Pursuant to Regulation 30 of the SEBI (Listing Obligations and Disclosure Requirement</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>49/14/14</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/3IINFOTECHLTD_02032026220734_Disclosure_HDFC_Signed.pdf</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/3IINFOLTD_2026-03-02.pdf</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951593</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>OSWALPUMPS</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Oswal Pumps Limited</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>₹22000.00 Cr</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Awarding of order(s)/contract(s)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>March 02, 2026 Listing Department Listing Department BSE Limited National Stock Exchange of India Limited Phiroze Jeejeebhoy Towers Exchange Plaza, Bandra Kurla Complex, Dalal Street Bandra (East) Mumbai – 400 001 Mumbai – 400051 Scrip Code: 544418 Name of Scrip: OSWALPUMPS Sub.: Disclosure under Regulation 30 of SEBI (Listing Obligations and Disclosure Requirements) Regulations, 2015 (‘Listing Regulations’) – Receipt of Order by Oswal Solar Energy Private Limited, Wholly Owned Subsidiary Dear S</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://nsearchives.nseindia.com/corporate/OSWALPUMPS_02032026151043_SELetterOSEPLPMKusumOPL02032026.pdf</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>downloads/nse_pdfs/OSWALPUMPS_2026-03-02.pdf</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>NSE_API</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-05-30T14:08:50.951600</t>
         </is>
       </c>
     </row>
